--- a/training_results_VIT_CIFAR_augumentacja.xlsx
+++ b/training_results_VIT_CIFAR_augumentacja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -549,9 +549,59 @@
         <v>cuda</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-05-25 23:00:01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CIFAR10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>64</v>
+      </c>
+      <c r="D4" t="str">
+        <v>64</v>
+      </c>
+      <c r="E4" t="str">
+        <v>20</v>
+      </c>
+      <c r="F4" t="str">
+        <v>20</v>
+      </c>
+      <c r="G4" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="H4" t="str">
+        <v>5</v>
+      </c>
+      <c r="I4" t="str">
+        <v>SGD</v>
+      </c>
+      <c r="J4" t="str">
+        <v>CosineAnnealingLR</v>
+      </c>
+      <c r="K4" t="str">
+        <v>98.93</v>
+      </c>
+      <c r="L4" t="str">
+        <v>97.64</v>
+      </c>
+      <c r="M4" t="str">
+        <v>92.91</v>
+      </c>
+      <c r="N4" t="str">
+        <v>0.5584</v>
+      </c>
+      <c r="O4" t="str">
+        <v>models/densenet_model_augumentacja_cifar10_64batch_20epochs_0.01lr.pth</v>
+      </c>
+      <c r="P4" t="str">
+        <v>cuda</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
   </ignoredErrors>
 </worksheet>
 </file>